--- a/samples/demo/서비스제공내역_소급.xlsx
+++ b/samples/demo/서비스제공내역_소급.xlsx
@@ -506,28 +506,28 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>윤파하</v>
+        <v>최사아</v>
       </c>
       <c r="B5" t="str">
-        <v>17.12.18</v>
+        <v>21.01.30</v>
       </c>
       <c r="C5" t="str">
-        <v>2026.04.01</v>
+        <v>2026.05.01</v>
       </c>
       <c r="D5" t="str">
-        <v>13:30</v>
+        <v>09:00</v>
       </c>
       <c r="E5" t="str">
-        <v>14:20</v>
+        <v>09:50</v>
       </c>
       <c r="F5" t="str">
-        <v>2026.04.01</v>
+        <v>2026.05.01</v>
       </c>
       <c r="G5" t="str">
-        <v>14:23</v>
+        <v>09:52</v>
       </c>
       <c r="H5" t="str">
-        <v>500900007049</v>
+        <v>500900007025</v>
       </c>
       <c r="I5" t="str">
         <v>65,000</v>
@@ -541,28 +541,28 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>백차카</v>
+        <v>정자차</v>
       </c>
       <c r="B6" t="str">
-        <v>18.08.05</v>
+        <v>20.07.14</v>
       </c>
       <c r="C6" t="str">
-        <v>2026.04.01</v>
+        <v>2026.05.01</v>
       </c>
       <c r="D6" t="str">
-        <v>16:00</v>
+        <v>09:50</v>
       </c>
       <c r="E6" t="str">
-        <v>16:50</v>
+        <v>10:40</v>
       </c>
       <c r="F6" t="str">
-        <v>2026.04.01</v>
+        <v>2026.05.01</v>
       </c>
       <c r="G6" t="str">
-        <v>16:52</v>
+        <v>10:42</v>
       </c>
       <c r="H6" t="str">
-        <v>500900007085</v>
+        <v>500900007033</v>
       </c>
       <c r="I6" t="str">
         <v>65,000</v>
@@ -576,28 +576,28 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>김가나</v>
+        <v>강카타</v>
       </c>
       <c r="B7" t="str">
-        <v>19.05.12</v>
+        <v>19.09.03</v>
       </c>
       <c r="C7" t="str">
-        <v>2026.04.02</v>
+        <v>2026.05.01</v>
       </c>
       <c r="D7" t="str">
-        <v>09:00</v>
+        <v>10:40</v>
       </c>
       <c r="E7" t="str">
-        <v>09:50</v>
+        <v>11:30</v>
       </c>
       <c r="F7" t="str">
-        <v>2026.04.02</v>
+        <v>2026.05.01</v>
       </c>
       <c r="G7" t="str">
-        <v>09:52</v>
+        <v>11:33</v>
       </c>
       <c r="H7" t="str">
-        <v>500900007001</v>
+        <v>500900007041</v>
       </c>
       <c r="I7" t="str">
         <v>65,000</v>
@@ -611,28 +611,28 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>이다라</v>
+        <v>조바사</v>
       </c>
       <c r="B8" t="str">
-        <v>20.03.08</v>
+        <v>19.04.11</v>
       </c>
       <c r="C8" t="str">
-        <v>2026.04.02</v>
+        <v>2026.05.01</v>
       </c>
       <c r="D8" t="str">
-        <v>09:50</v>
+        <v>13:30</v>
       </c>
       <c r="E8" t="str">
-        <v>10:40</v>
+        <v>14:20</v>
       </c>
       <c r="F8" t="str">
-        <v>2026.04.02</v>
+        <v>2026.05.01</v>
       </c>
       <c r="G8" t="str">
-        <v>10:42</v>
+        <v>14:23</v>
       </c>
       <c r="H8" t="str">
-        <v>500900007009</v>
+        <v>500900007069</v>
       </c>
       <c r="I8" t="str">
         <v>65,000</v>
@@ -646,28 +646,28 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>박마바</v>
+        <v>한아자</v>
       </c>
       <c r="B9" t="str">
-        <v>18.11.22</v>
+        <v>20.10.21</v>
       </c>
       <c r="C9" t="str">
-        <v>2026.04.02</v>
+        <v>2026.05.01</v>
       </c>
       <c r="D9" t="str">
-        <v>10:40</v>
+        <v>15:10</v>
       </c>
       <c r="E9" t="str">
-        <v>11:30</v>
+        <v>16:00</v>
       </c>
       <c r="F9" t="str">
-        <v>2026.04.02</v>
+        <v>2026.05.01</v>
       </c>
       <c r="G9" t="str">
-        <v>11:32</v>
+        <v>16:03</v>
       </c>
       <c r="H9" t="str">
-        <v>500900007017</v>
+        <v>500900007077</v>
       </c>
       <c r="I9" t="str">
         <v>65,000</v>
@@ -681,28 +681,28 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>임가다</v>
+        <v>김가나</v>
       </c>
       <c r="B10" t="str">
-        <v>20.02.25</v>
+        <v>19.05.12</v>
       </c>
       <c r="C10" t="str">
-        <v>2026.04.02</v>
+        <v>2026.05.04</v>
       </c>
       <c r="D10" t="str">
-        <v>13:30</v>
+        <v>09:00</v>
       </c>
       <c r="E10" t="str">
-        <v>14:20</v>
+        <v>09:50</v>
       </c>
       <c r="F10" t="str">
-        <v>2026.04.02</v>
+        <v>2026.05.04</v>
       </c>
       <c r="G10" t="str">
-        <v>14:22</v>
+        <v>09:53</v>
       </c>
       <c r="H10" t="str">
-        <v>500900007053</v>
+        <v>500900007001</v>
       </c>
       <c r="I10" t="str">
         <v>65,000</v>
@@ -716,28 +716,28 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>송라마</v>
+        <v>이다라</v>
       </c>
       <c r="B11" t="str">
-        <v>21.06.07</v>
+        <v>20.03.08</v>
       </c>
       <c r="C11" t="str">
-        <v>2026.04.02</v>
+        <v>2026.05.04</v>
       </c>
       <c r="D11" t="str">
-        <v>14:20</v>
+        <v>09:50</v>
       </c>
       <c r="E11" t="str">
-        <v>15:10</v>
+        <v>10:40</v>
       </c>
       <c r="F11" t="str">
-        <v>2026.04.02</v>
+        <v>2026.05.04</v>
       </c>
       <c r="G11" t="str">
-        <v>15:13</v>
+        <v>10:43</v>
       </c>
       <c r="H11" t="str">
-        <v>500900007061</v>
+        <v>500900007009</v>
       </c>
       <c r="I11" t="str">
         <v>65,000</v>
@@ -751,28 +751,28 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>최사아</v>
+        <v>박마바</v>
       </c>
       <c r="B12" t="str">
-        <v>21.01.30</v>
+        <v>18.11.22</v>
       </c>
       <c r="C12" t="str">
-        <v>2026.04.03</v>
+        <v>2026.05.04</v>
       </c>
       <c r="D12" t="str">
-        <v>09:00</v>
+        <v>10:40</v>
       </c>
       <c r="E12" t="str">
-        <v>09:50</v>
+        <v>11:30</v>
       </c>
       <c r="F12" t="str">
-        <v>2026.04.03</v>
+        <v>2026.05.04</v>
       </c>
       <c r="G12" t="str">
-        <v>09:53</v>
+        <v>11:33</v>
       </c>
       <c r="H12" t="str">
-        <v>500900007025</v>
+        <v>500900007017</v>
       </c>
       <c r="I12" t="str">
         <v>65,000</v>
@@ -786,28 +786,28 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>정자차</v>
+        <v>임가다</v>
       </c>
       <c r="B13" t="str">
-        <v>20.07.14</v>
+        <v>20.02.25</v>
       </c>
       <c r="C13" t="str">
-        <v>2026.04.03</v>
+        <v>2026.05.04</v>
       </c>
       <c r="D13" t="str">
-        <v>09:50</v>
+        <v>13:30</v>
       </c>
       <c r="E13" t="str">
-        <v>10:40</v>
+        <v>14:20</v>
       </c>
       <c r="F13" t="str">
-        <v>2026.04.03</v>
+        <v>2026.05.04</v>
       </c>
       <c r="G13" t="str">
-        <v>10:42</v>
+        <v>14:23</v>
       </c>
       <c r="H13" t="str">
-        <v>500900007033</v>
+        <v>500900007053</v>
       </c>
       <c r="I13" t="str">
         <v>65,000</v>
@@ -821,28 +821,28 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>강카타</v>
+        <v>송라마</v>
       </c>
       <c r="B14" t="str">
-        <v>19.09.03</v>
+        <v>21.06.07</v>
       </c>
       <c r="C14" t="str">
-        <v>2026.04.03</v>
+        <v>2026.05.04</v>
       </c>
       <c r="D14" t="str">
-        <v>10:40</v>
+        <v>14:20</v>
       </c>
       <c r="E14" t="str">
-        <v>11:30</v>
+        <v>15:10</v>
       </c>
       <c r="F14" t="str">
-        <v>2026.04.03</v>
+        <v>2026.05.04</v>
       </c>
       <c r="G14" t="str">
-        <v>11:32</v>
+        <v>15:12</v>
       </c>
       <c r="H14" t="str">
-        <v>500900007041</v>
+        <v>500900007061</v>
       </c>
       <c r="I14" t="str">
         <v>65,000</v>
@@ -856,28 +856,28 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>조바사</v>
+        <v>최사아</v>
       </c>
       <c r="B15" t="str">
-        <v>19.04.11</v>
+        <v>21.01.30</v>
       </c>
       <c r="C15" t="str">
-        <v>2026.04.03</v>
+        <v>2026.05.05</v>
       </c>
       <c r="D15" t="str">
-        <v>13:30</v>
+        <v>09:00</v>
       </c>
       <c r="E15" t="str">
-        <v>14:20</v>
+        <v>09:50</v>
       </c>
       <c r="F15" t="str">
-        <v>2026.04.03</v>
+        <v>2026.05.05</v>
       </c>
       <c r="G15" t="str">
-        <v>14:23</v>
+        <v>09:53</v>
       </c>
       <c r="H15" t="str">
-        <v>500900007069</v>
+        <v>500900007026</v>
       </c>
       <c r="I15" t="str">
         <v>65,000</v>
@@ -891,28 +891,28 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>한아자</v>
+        <v>정자차</v>
       </c>
       <c r="B16" t="str">
-        <v>20.10.21</v>
+        <v>20.07.14</v>
       </c>
       <c r="C16" t="str">
-        <v>2026.04.03</v>
+        <v>2026.05.05</v>
       </c>
       <c r="D16" t="str">
-        <v>15:10</v>
+        <v>09:50</v>
       </c>
       <c r="E16" t="str">
-        <v>16:00</v>
+        <v>10:40</v>
       </c>
       <c r="F16" t="str">
-        <v>2026.04.03</v>
+        <v>2026.05.05</v>
       </c>
       <c r="G16" t="str">
-        <v>16:02</v>
+        <v>10:43</v>
       </c>
       <c r="H16" t="str">
-        <v>500900007077</v>
+        <v>500900007034</v>
       </c>
       <c r="I16" t="str">
         <v>65,000</v>
@@ -926,28 +926,28 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>김가나</v>
+        <v>강카타</v>
       </c>
       <c r="B17" t="str">
-        <v>19.05.12</v>
+        <v>19.09.03</v>
       </c>
       <c r="C17" t="str">
-        <v>2026.04.06</v>
+        <v>2026.05.05</v>
       </c>
       <c r="D17" t="str">
-        <v>09:00</v>
+        <v>10:40</v>
       </c>
       <c r="E17" t="str">
-        <v>09:50</v>
+        <v>11:30</v>
       </c>
       <c r="F17" t="str">
-        <v>2026.04.06</v>
+        <v>2026.05.05</v>
       </c>
       <c r="G17" t="str">
-        <v>09:53</v>
+        <v>11:33</v>
       </c>
       <c r="H17" t="str">
-        <v>500900007002</v>
+        <v>500900007042</v>
       </c>
       <c r="I17" t="str">
         <v>65,000</v>
@@ -961,28 +961,28 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>이다라</v>
+        <v>조바사</v>
       </c>
       <c r="B18" t="str">
-        <v>20.03.08</v>
+        <v>19.04.11</v>
       </c>
       <c r="C18" t="str">
-        <v>2026.04.06</v>
+        <v>2026.05.05</v>
       </c>
       <c r="D18" t="str">
-        <v>09:50</v>
+        <v>13:30</v>
       </c>
       <c r="E18" t="str">
-        <v>10:40</v>
+        <v>14:20</v>
       </c>
       <c r="F18" t="str">
-        <v>2026.04.06</v>
+        <v>2026.05.05</v>
       </c>
       <c r="G18" t="str">
-        <v>10:42</v>
+        <v>14:22</v>
       </c>
       <c r="H18" t="str">
-        <v>500900007010</v>
+        <v>500900007070</v>
       </c>
       <c r="I18" t="str">
         <v>65,000</v>
@@ -996,28 +996,28 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>박마바</v>
+        <v>한아자</v>
       </c>
       <c r="B19" t="str">
-        <v>18.11.22</v>
+        <v>20.10.21</v>
       </c>
       <c r="C19" t="str">
-        <v>2026.04.06</v>
+        <v>2026.05.05</v>
       </c>
       <c r="D19" t="str">
-        <v>10:40</v>
+        <v>15:10</v>
       </c>
       <c r="E19" t="str">
-        <v>11:30</v>
+        <v>16:00</v>
       </c>
       <c r="F19" t="str">
-        <v>2026.04.06</v>
+        <v>2026.05.05</v>
       </c>
       <c r="G19" t="str">
-        <v>11:32</v>
+        <v>16:03</v>
       </c>
       <c r="H19" t="str">
-        <v>500900007018</v>
+        <v>500900007078</v>
       </c>
       <c r="I19" t="str">
         <v>65,000</v>
@@ -1031,13 +1031,13 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>임가다</v>
+        <v>윤파하</v>
       </c>
       <c r="B20" t="str">
-        <v>20.02.25</v>
+        <v>17.12.18</v>
       </c>
       <c r="C20" t="str">
-        <v>2026.04.06</v>
+        <v>2026.05.06</v>
       </c>
       <c r="D20" t="str">
         <v>13:30</v>
@@ -1046,13 +1046,13 @@
         <v>14:20</v>
       </c>
       <c r="F20" t="str">
-        <v>2026.04.06</v>
+        <v>2026.05.06</v>
       </c>
       <c r="G20" t="str">
-        <v>14:22</v>
+        <v>14:23</v>
       </c>
       <c r="H20" t="str">
-        <v>500900007054</v>
+        <v>500900007049</v>
       </c>
       <c r="I20" t="str">
         <v>65,000</v>
@@ -1066,28 +1066,28 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>송라마</v>
+        <v>백차카</v>
       </c>
       <c r="B21" t="str">
-        <v>21.06.07</v>
+        <v>18.08.05</v>
       </c>
       <c r="C21" t="str">
-        <v>2026.04.06</v>
+        <v>2026.05.06</v>
       </c>
       <c r="D21" t="str">
-        <v>14:20</v>
+        <v>16:00</v>
       </c>
       <c r="E21" t="str">
-        <v>15:10</v>
+        <v>16:50</v>
       </c>
       <c r="F21" t="str">
-        <v>2026.04.06</v>
+        <v>2026.05.06</v>
       </c>
       <c r="G21" t="str">
-        <v>15:12</v>
+        <v>16:52</v>
       </c>
       <c r="H21" t="str">
-        <v>500900007062</v>
+        <v>500900007085</v>
       </c>
       <c r="I21" t="str">
         <v>65,000</v>
@@ -1101,13 +1101,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>최사아</v>
+        <v>김가나</v>
       </c>
       <c r="B22" t="str">
-        <v>21.01.30</v>
+        <v>19.05.12</v>
       </c>
       <c r="C22" t="str">
-        <v>2026.04.07</v>
+        <v>2026.05.07</v>
       </c>
       <c r="D22" t="str">
         <v>09:00</v>
@@ -1116,13 +1116,13 @@
         <v>09:50</v>
       </c>
       <c r="F22" t="str">
-        <v>2026.04.07</v>
+        <v>2026.05.07</v>
       </c>
       <c r="G22" t="str">
-        <v>09:52</v>
+        <v>09:53</v>
       </c>
       <c r="H22" t="str">
-        <v>500900007026</v>
+        <v>500900007002</v>
       </c>
       <c r="I22" t="str">
         <v>65,000</v>
@@ -1136,13 +1136,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>정자차</v>
+        <v>이다라</v>
       </c>
       <c r="B23" t="str">
-        <v>20.07.14</v>
+        <v>20.03.08</v>
       </c>
       <c r="C23" t="str">
-        <v>2026.04.07</v>
+        <v>2026.05.07</v>
       </c>
       <c r="D23" t="str">
         <v>09:50</v>
@@ -1151,13 +1151,13 @@
         <v>10:40</v>
       </c>
       <c r="F23" t="str">
-        <v>2026.04.07</v>
+        <v>2026.05.07</v>
       </c>
       <c r="G23" t="str">
-        <v>10:42</v>
+        <v>10:43</v>
       </c>
       <c r="H23" t="str">
-        <v>500900007034</v>
+        <v>500900007010</v>
       </c>
       <c r="I23" t="str">
         <v>65,000</v>
@@ -1171,13 +1171,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>강카타</v>
+        <v>박마바</v>
       </c>
       <c r="B24" t="str">
-        <v>19.09.03</v>
+        <v>18.11.22</v>
       </c>
       <c r="C24" t="str">
-        <v>2026.04.07</v>
+        <v>2026.05.07</v>
       </c>
       <c r="D24" t="str">
         <v>10:40</v>
@@ -1186,13 +1186,13 @@
         <v>11:30</v>
       </c>
       <c r="F24" t="str">
-        <v>2026.04.07</v>
+        <v>2026.05.07</v>
       </c>
       <c r="G24" t="str">
-        <v>11:33</v>
+        <v>11:32</v>
       </c>
       <c r="H24" t="str">
-        <v>500900007042</v>
+        <v>500900007018</v>
       </c>
       <c r="I24" t="str">
         <v>65,000</v>
@@ -1206,13 +1206,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>조바사</v>
+        <v>임가다</v>
       </c>
       <c r="B25" t="str">
-        <v>19.04.11</v>
+        <v>20.02.25</v>
       </c>
       <c r="C25" t="str">
-        <v>2026.04.07</v>
+        <v>2026.05.07</v>
       </c>
       <c r="D25" t="str">
         <v>13:30</v>
@@ -1221,13 +1221,13 @@
         <v>14:20</v>
       </c>
       <c r="F25" t="str">
-        <v>2026.04.07</v>
+        <v>2026.05.07</v>
       </c>
       <c r="G25" t="str">
-        <v>14:23</v>
+        <v>14:22</v>
       </c>
       <c r="H25" t="str">
-        <v>500900007070</v>
+        <v>500900007054</v>
       </c>
       <c r="I25" t="str">
         <v>65,000</v>
@@ -1241,28 +1241,28 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>한아자</v>
+        <v>송라마</v>
       </c>
       <c r="B26" t="str">
-        <v>20.10.21</v>
+        <v>21.06.07</v>
       </c>
       <c r="C26" t="str">
-        <v>2026.04.07</v>
+        <v>2026.05.07</v>
       </c>
       <c r="D26" t="str">
+        <v>14:20</v>
+      </c>
+      <c r="E26" t="str">
         <v>15:10</v>
       </c>
-      <c r="E26" t="str">
-        <v>16:00</v>
-      </c>
       <c r="F26" t="str">
-        <v>2026.04.07</v>
+        <v>2026.05.07</v>
       </c>
       <c r="G26" t="str">
-        <v>16:03</v>
+        <v>15:13</v>
       </c>
       <c r="H26" t="str">
-        <v>500900007078</v>
+        <v>500900007062</v>
       </c>
       <c r="I26" t="str">
         <v>65,000</v>
@@ -1276,28 +1276,28 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>윤파하</v>
+        <v>최사아</v>
       </c>
       <c r="B27" t="str">
-        <v>17.12.18</v>
+        <v>21.01.30</v>
       </c>
       <c r="C27" t="str">
-        <v>2026.04.08</v>
+        <v>2026.05.08</v>
       </c>
       <c r="D27" t="str">
-        <v>13:30</v>
+        <v>09:00</v>
       </c>
       <c r="E27" t="str">
-        <v>14:20</v>
+        <v>09:50</v>
       </c>
       <c r="F27" t="str">
-        <v>2026.04.08</v>
+        <v>2026.05.08</v>
       </c>
       <c r="G27" t="str">
-        <v>14:23</v>
+        <v>09:52</v>
       </c>
       <c r="H27" t="str">
-        <v>500900007050</v>
+        <v>500900007027</v>
       </c>
       <c r="I27" t="str">
         <v>65,000</v>
@@ -1311,28 +1311,28 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>백차카</v>
+        <v>정자차</v>
       </c>
       <c r="B28" t="str">
-        <v>18.08.05</v>
+        <v>20.07.14</v>
       </c>
       <c r="C28" t="str">
-        <v>2026.04.08</v>
+        <v>2026.05.08</v>
       </c>
       <c r="D28" t="str">
-        <v>16:00</v>
+        <v>09:50</v>
       </c>
       <c r="E28" t="str">
-        <v>16:50</v>
+        <v>10:40</v>
       </c>
       <c r="F28" t="str">
-        <v>2026.04.08</v>
+        <v>2026.05.08</v>
       </c>
       <c r="G28" t="str">
-        <v>16:53</v>
+        <v>10:43</v>
       </c>
       <c r="H28" t="str">
-        <v>500900007086</v>
+        <v>500900007035</v>
       </c>
       <c r="I28" t="str">
         <v>65,000</v>
@@ -1346,28 +1346,28 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>김가나</v>
+        <v>강카타</v>
       </c>
       <c r="B29" t="str">
-        <v>19.05.12</v>
+        <v>19.09.03</v>
       </c>
       <c r="C29" t="str">
-        <v>2026.04.09</v>
+        <v>2026.05.08</v>
       </c>
       <c r="D29" t="str">
-        <v>09:00</v>
+        <v>10:40</v>
       </c>
       <c r="E29" t="str">
-        <v>09:50</v>
+        <v>11:30</v>
       </c>
       <c r="F29" t="str">
-        <v>2026.04.09</v>
+        <v>2026.05.08</v>
       </c>
       <c r="G29" t="str">
-        <v>09:52</v>
+        <v>11:33</v>
       </c>
       <c r="H29" t="str">
-        <v>500900007003</v>
+        <v>500900007043</v>
       </c>
       <c r="I29" t="str">
         <v>65,000</v>
@@ -1381,28 +1381,28 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>이다라</v>
+        <v>조바사</v>
       </c>
       <c r="B30" t="str">
-        <v>20.03.08</v>
+        <v>19.04.11</v>
       </c>
       <c r="C30" t="str">
-        <v>2026.04.09</v>
+        <v>2026.05.08</v>
       </c>
       <c r="D30" t="str">
-        <v>09:50</v>
+        <v>13:30</v>
       </c>
       <c r="E30" t="str">
-        <v>10:40</v>
+        <v>14:20</v>
       </c>
       <c r="F30" t="str">
-        <v>2026.04.09</v>
+        <v>2026.05.08</v>
       </c>
       <c r="G30" t="str">
-        <v>10:42</v>
+        <v>14:22</v>
       </c>
       <c r="H30" t="str">
-        <v>500900007011</v>
+        <v>500900007071</v>
       </c>
       <c r="I30" t="str">
         <v>65,000</v>
@@ -1416,28 +1416,28 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>박마바</v>
+        <v>한아자</v>
       </c>
       <c r="B31" t="str">
-        <v>18.11.22</v>
+        <v>20.10.21</v>
       </c>
       <c r="C31" t="str">
-        <v>2026.04.09</v>
+        <v>2026.05.08</v>
       </c>
       <c r="D31" t="str">
-        <v>10:40</v>
+        <v>15:10</v>
       </c>
       <c r="E31" t="str">
-        <v>11:30</v>
+        <v>16:00</v>
       </c>
       <c r="F31" t="str">
-        <v>2026.04.09</v>
+        <v>2026.05.08</v>
       </c>
       <c r="G31" t="str">
-        <v>11:32</v>
+        <v>16:03</v>
       </c>
       <c r="H31" t="str">
-        <v>500900007019</v>
+        <v>500900007079</v>
       </c>
       <c r="I31" t="str">
         <v>65,000</v>
@@ -1451,28 +1451,28 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>임가다</v>
+        <v>김가나</v>
       </c>
       <c r="B32" t="str">
-        <v>20.02.25</v>
+        <v>19.05.12</v>
       </c>
       <c r="C32" t="str">
-        <v>2026.04.09</v>
+        <v>2026.05.11</v>
       </c>
       <c r="D32" t="str">
-        <v>13:30</v>
+        <v>09:00</v>
       </c>
       <c r="E32" t="str">
-        <v>14:20</v>
+        <v>09:50</v>
       </c>
       <c r="F32" t="str">
-        <v>2026.04.09</v>
+        <v>2026.05.11</v>
       </c>
       <c r="G32" t="str">
-        <v>14:22</v>
+        <v>09:53</v>
       </c>
       <c r="H32" t="str">
-        <v>500900007055</v>
+        <v>500900007003</v>
       </c>
       <c r="I32" t="str">
         <v>65,000</v>
@@ -1486,28 +1486,28 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>송라마</v>
+        <v>이다라</v>
       </c>
       <c r="B33" t="str">
-        <v>21.06.07</v>
+        <v>20.03.08</v>
       </c>
       <c r="C33" t="str">
-        <v>2026.04.09</v>
+        <v>2026.05.11</v>
       </c>
       <c r="D33" t="str">
-        <v>14:20</v>
+        <v>09:50</v>
       </c>
       <c r="E33" t="str">
-        <v>15:10</v>
+        <v>10:40</v>
       </c>
       <c r="F33" t="str">
-        <v>2026.04.09</v>
+        <v>2026.05.11</v>
       </c>
       <c r="G33" t="str">
-        <v>15:13</v>
+        <v>10:42</v>
       </c>
       <c r="H33" t="str">
-        <v>500900007063</v>
+        <v>500900007011</v>
       </c>
       <c r="I33" t="str">
         <v>65,000</v>
@@ -1521,28 +1521,28 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>최사아</v>
+        <v>박마바</v>
       </c>
       <c r="B34" t="str">
-        <v>21.01.30</v>
+        <v>18.11.22</v>
       </c>
       <c r="C34" t="str">
-        <v>2026.04.10</v>
+        <v>2026.05.11</v>
       </c>
       <c r="D34" t="str">
-        <v>09:00</v>
+        <v>10:40</v>
       </c>
       <c r="E34" t="str">
-        <v>09:50</v>
+        <v>11:30</v>
       </c>
       <c r="F34" t="str">
-        <v>2026.04.10</v>
+        <v>2026.05.11</v>
       </c>
       <c r="G34" t="str">
-        <v>09:52</v>
+        <v>11:32</v>
       </c>
       <c r="H34" t="str">
-        <v>500900007027</v>
+        <v>500900007019</v>
       </c>
       <c r="I34" t="str">
         <v>65,000</v>
@@ -1556,28 +1556,28 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>정자차</v>
+        <v>임가다</v>
       </c>
       <c r="B35" t="str">
-        <v>20.07.14</v>
+        <v>20.02.25</v>
       </c>
       <c r="C35" t="str">
-        <v>2026.04.10</v>
+        <v>2026.05.11</v>
       </c>
       <c r="D35" t="str">
-        <v>09:50</v>
+        <v>13:30</v>
       </c>
       <c r="E35" t="str">
-        <v>10:40</v>
+        <v>14:20</v>
       </c>
       <c r="F35" t="str">
-        <v>2026.04.10</v>
+        <v>2026.05.11</v>
       </c>
       <c r="G35" t="str">
-        <v>10:42</v>
+        <v>14:23</v>
       </c>
       <c r="H35" t="str">
-        <v>500900007035</v>
+        <v>500900007055</v>
       </c>
       <c r="I35" t="str">
         <v>65,000</v>
@@ -1591,28 +1591,28 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>강카타</v>
+        <v>송라마</v>
       </c>
       <c r="B36" t="str">
-        <v>19.09.03</v>
+        <v>21.06.07</v>
       </c>
       <c r="C36" t="str">
-        <v>2026.04.10</v>
+        <v>2026.05.11</v>
       </c>
       <c r="D36" t="str">
-        <v>10:40</v>
+        <v>14:20</v>
       </c>
       <c r="E36" t="str">
-        <v>11:30</v>
+        <v>15:10</v>
       </c>
       <c r="F36" t="str">
-        <v>2026.04.10</v>
+        <v>2026.05.11</v>
       </c>
       <c r="G36" t="str">
-        <v>11:33</v>
+        <v>15:13</v>
       </c>
       <c r="H36" t="str">
-        <v>500900007043</v>
+        <v>500900007063</v>
       </c>
       <c r="I36" t="str">
         <v>65,000</v>
@@ -1626,28 +1626,28 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>조바사</v>
+        <v>최사아</v>
       </c>
       <c r="B37" t="str">
-        <v>19.04.11</v>
+        <v>21.01.30</v>
       </c>
       <c r="C37" t="str">
-        <v>2026.04.10</v>
+        <v>2026.05.12</v>
       </c>
       <c r="D37" t="str">
-        <v>13:30</v>
+        <v>09:00</v>
       </c>
       <c r="E37" t="str">
-        <v>14:20</v>
+        <v>09:50</v>
       </c>
       <c r="F37" t="str">
-        <v>2026.04.10</v>
+        <v>2026.05.12</v>
       </c>
       <c r="G37" t="str">
-        <v>14:22</v>
+        <v>09:52</v>
       </c>
       <c r="H37" t="str">
-        <v>500900007071</v>
+        <v>500900007028</v>
       </c>
       <c r="I37" t="str">
         <v>65,000</v>
@@ -1661,28 +1661,28 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>한아자</v>
+        <v>정자차</v>
       </c>
       <c r="B38" t="str">
-        <v>20.10.21</v>
+        <v>20.07.14</v>
       </c>
       <c r="C38" t="str">
-        <v>2026.04.10</v>
+        <v>2026.05.12</v>
       </c>
       <c r="D38" t="str">
-        <v>15:10</v>
+        <v>09:50</v>
       </c>
       <c r="E38" t="str">
-        <v>16:00</v>
+        <v>10:40</v>
       </c>
       <c r="F38" t="str">
-        <v>2026.04.10</v>
+        <v>2026.05.12</v>
       </c>
       <c r="G38" t="str">
-        <v>16:02</v>
+        <v>10:42</v>
       </c>
       <c r="H38" t="str">
-        <v>500900007079</v>
+        <v>500900007036</v>
       </c>
       <c r="I38" t="str">
         <v>65,000</v>
@@ -1696,28 +1696,28 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>김가나</v>
+        <v>강카타</v>
       </c>
       <c r="B39" t="str">
-        <v>19.05.12</v>
+        <v>19.09.03</v>
       </c>
       <c r="C39" t="str">
-        <v>2026.04.13</v>
+        <v>2026.05.12</v>
       </c>
       <c r="D39" t="str">
-        <v>09:00</v>
+        <v>10:40</v>
       </c>
       <c r="E39" t="str">
-        <v>09:50</v>
+        <v>11:30</v>
       </c>
       <c r="F39" t="str">
-        <v>2026.04.13</v>
+        <v>2026.05.12</v>
       </c>
       <c r="G39" t="str">
-        <v>09:52</v>
+        <v>11:33</v>
       </c>
       <c r="H39" t="str">
-        <v>500900007004</v>
+        <v>500900007044</v>
       </c>
       <c r="I39" t="str">
         <v>65,000</v>
@@ -1731,28 +1731,28 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>이다라</v>
+        <v>조바사</v>
       </c>
       <c r="B40" t="str">
-        <v>20.03.08</v>
+        <v>19.04.11</v>
       </c>
       <c r="C40" t="str">
-        <v>2026.04.13</v>
+        <v>2026.05.12</v>
       </c>
       <c r="D40" t="str">
-        <v>09:50</v>
+        <v>13:30</v>
       </c>
       <c r="E40" t="str">
-        <v>10:40</v>
+        <v>14:20</v>
       </c>
       <c r="F40" t="str">
-        <v>2026.04.13</v>
+        <v>2026.05.12</v>
       </c>
       <c r="G40" t="str">
-        <v>10:42</v>
+        <v>14:22</v>
       </c>
       <c r="H40" t="str">
-        <v>500900007012</v>
+        <v>500900007072</v>
       </c>
       <c r="I40" t="str">
         <v>65,000</v>
@@ -1766,28 +1766,28 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>박마바</v>
+        <v>한아자</v>
       </c>
       <c r="B41" t="str">
-        <v>18.11.22</v>
+        <v>20.10.21</v>
       </c>
       <c r="C41" t="str">
-        <v>2026.04.13</v>
+        <v>2026.05.12</v>
       </c>
       <c r="D41" t="str">
-        <v>10:40</v>
+        <v>15:10</v>
       </c>
       <c r="E41" t="str">
-        <v>11:30</v>
+        <v>16:00</v>
       </c>
       <c r="F41" t="str">
-        <v>2026.04.13</v>
+        <v>2026.05.12</v>
       </c>
       <c r="G41" t="str">
-        <v>11:32</v>
+        <v>16:02</v>
       </c>
       <c r="H41" t="str">
-        <v>500900007020</v>
+        <v>500900007080</v>
       </c>
       <c r="I41" t="str">
         <v>65,000</v>
@@ -1801,13 +1801,13 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>임가다</v>
+        <v>윤파하</v>
       </c>
       <c r="B42" t="str">
-        <v>20.02.25</v>
+        <v>17.12.18</v>
       </c>
       <c r="C42" t="str">
-        <v>2026.04.13</v>
+        <v>2026.05.13</v>
       </c>
       <c r="D42" t="str">
         <v>13:30</v>
@@ -1816,13 +1816,13 @@
         <v>14:20</v>
       </c>
       <c r="F42" t="str">
-        <v>2026.04.13</v>
+        <v>2026.05.13</v>
       </c>
       <c r="G42" t="str">
         <v>14:22</v>
       </c>
       <c r="H42" t="str">
-        <v>500900007056</v>
+        <v>500900007050</v>
       </c>
       <c r="I42" t="str">
         <v>65,000</v>
@@ -1836,28 +1836,28 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>송라마</v>
+        <v>백차카</v>
       </c>
       <c r="B43" t="str">
-        <v>21.06.07</v>
+        <v>18.08.05</v>
       </c>
       <c r="C43" t="str">
-        <v>2026.04.13</v>
+        <v>2026.05.13</v>
       </c>
       <c r="D43" t="str">
-        <v>14:20</v>
+        <v>16:00</v>
       </c>
       <c r="E43" t="str">
-        <v>15:10</v>
+        <v>16:50</v>
       </c>
       <c r="F43" t="str">
-        <v>2026.04.13</v>
+        <v>2026.05.13</v>
       </c>
       <c r="G43" t="str">
-        <v>15:13</v>
+        <v>16:53</v>
       </c>
       <c r="H43" t="str">
-        <v>500900007064</v>
+        <v>500900007086</v>
       </c>
       <c r="I43" t="str">
         <v>65,000</v>
@@ -1871,13 +1871,13 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>최사아</v>
+        <v>김가나</v>
       </c>
       <c r="B44" t="str">
-        <v>21.01.30</v>
+        <v>19.05.12</v>
       </c>
       <c r="C44" t="str">
-        <v>2026.04.14</v>
+        <v>2026.05.14</v>
       </c>
       <c r="D44" t="str">
         <v>09:00</v>
@@ -1886,13 +1886,13 @@
         <v>09:50</v>
       </c>
       <c r="F44" t="str">
-        <v>2026.04.14</v>
+        <v>2026.05.14</v>
       </c>
       <c r="G44" t="str">
         <v>09:52</v>
       </c>
       <c r="H44" t="str">
-        <v>500900007028</v>
+        <v>500900007004</v>
       </c>
       <c r="I44" t="str">
         <v>65,000</v>
@@ -1906,13 +1906,13 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>정자차</v>
+        <v>이다라</v>
       </c>
       <c r="B45" t="str">
-        <v>20.07.14</v>
+        <v>20.03.08</v>
       </c>
       <c r="C45" t="str">
-        <v>2026.04.14</v>
+        <v>2026.05.14</v>
       </c>
       <c r="D45" t="str">
         <v>09:50</v>
@@ -1921,13 +1921,13 @@
         <v>10:40</v>
       </c>
       <c r="F45" t="str">
-        <v>2026.04.14</v>
+        <v>2026.05.14</v>
       </c>
       <c r="G45" t="str">
-        <v>10:42</v>
+        <v>10:43</v>
       </c>
       <c r="H45" t="str">
-        <v>500900007036</v>
+        <v>500900007012</v>
       </c>
       <c r="I45" t="str">
         <v>65,000</v>
@@ -1941,13 +1941,13 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>강카타</v>
+        <v>박마바</v>
       </c>
       <c r="B46" t="str">
-        <v>19.09.03</v>
+        <v>18.11.22</v>
       </c>
       <c r="C46" t="str">
-        <v>2026.04.14</v>
+        <v>2026.05.14</v>
       </c>
       <c r="D46" t="str">
         <v>10:40</v>
@@ -1956,13 +1956,13 @@
         <v>11:30</v>
       </c>
       <c r="F46" t="str">
-        <v>2026.04.14</v>
+        <v>2026.05.14</v>
       </c>
       <c r="G46" t="str">
-        <v>11:33</v>
+        <v>11:32</v>
       </c>
       <c r="H46" t="str">
-        <v>500900007044</v>
+        <v>500900007020</v>
       </c>
       <c r="I46" t="str">
         <v>65,000</v>
@@ -1976,13 +1976,13 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>조바사</v>
+        <v>임가다</v>
       </c>
       <c r="B47" t="str">
-        <v>19.04.11</v>
+        <v>20.02.25</v>
       </c>
       <c r="C47" t="str">
-        <v>2026.04.14</v>
+        <v>2026.05.14</v>
       </c>
       <c r="D47" t="str">
         <v>13:30</v>
@@ -1991,13 +1991,13 @@
         <v>14:20</v>
       </c>
       <c r="F47" t="str">
-        <v>2026.04.14</v>
+        <v>2026.05.14</v>
       </c>
       <c r="G47" t="str">
-        <v>14:23</v>
+        <v>14:22</v>
       </c>
       <c r="H47" t="str">
-        <v>500900007072</v>
+        <v>500900007056</v>
       </c>
       <c r="I47" t="str">
         <v>65,000</v>
@@ -2011,28 +2011,28 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>한아자</v>
+        <v>송라마</v>
       </c>
       <c r="B48" t="str">
-        <v>20.10.21</v>
+        <v>21.06.07</v>
       </c>
       <c r="C48" t="str">
-        <v>2026.04.14</v>
+        <v>2026.05.14</v>
       </c>
       <c r="D48" t="str">
+        <v>14:20</v>
+      </c>
+      <c r="E48" t="str">
         <v>15:10</v>
       </c>
-      <c r="E48" t="str">
-        <v>16:00</v>
-      </c>
       <c r="F48" t="str">
-        <v>2026.04.14</v>
+        <v>2026.05.14</v>
       </c>
       <c r="G48" t="str">
-        <v>16:02</v>
+        <v>15:12</v>
       </c>
       <c r="H48" t="str">
-        <v>500900007080</v>
+        <v>500900007064</v>
       </c>
       <c r="I48" t="str">
         <v>65,000</v>
@@ -2046,28 +2046,28 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>윤파하</v>
+        <v>최사아</v>
       </c>
       <c r="B49" t="str">
-        <v>17.12.18</v>
+        <v>21.01.30</v>
       </c>
       <c r="C49" t="str">
-        <v>2026.04.15</v>
+        <v>2026.05.15</v>
       </c>
       <c r="D49" t="str">
-        <v>13:30</v>
+        <v>09:00</v>
       </c>
       <c r="E49" t="str">
-        <v>14:20</v>
+        <v>09:50</v>
       </c>
       <c r="F49" t="str">
-        <v>2026.04.15</v>
+        <v>2026.05.15</v>
       </c>
       <c r="G49" t="str">
-        <v>14:22</v>
+        <v>09:53</v>
       </c>
       <c r="H49" t="str">
-        <v>500900007051</v>
+        <v>500900007029</v>
       </c>
       <c r="I49" t="str">
         <v>65,000</v>
@@ -2081,28 +2081,28 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>백차카</v>
+        <v>정자차</v>
       </c>
       <c r="B50" t="str">
-        <v>18.08.05</v>
+        <v>20.07.14</v>
       </c>
       <c r="C50" t="str">
-        <v>2026.04.15</v>
+        <v>2026.05.15</v>
       </c>
       <c r="D50" t="str">
-        <v>16:00</v>
+        <v>09:50</v>
       </c>
       <c r="E50" t="str">
-        <v>16:50</v>
+        <v>10:40</v>
       </c>
       <c r="F50" t="str">
-        <v>2026.04.15</v>
+        <v>2026.05.15</v>
       </c>
       <c r="G50" t="str">
-        <v>16:52</v>
+        <v>10:43</v>
       </c>
       <c r="H50" t="str">
-        <v>500900007087</v>
+        <v>500900007037</v>
       </c>
       <c r="I50" t="str">
         <v>65,000</v>
@@ -2116,28 +2116,28 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>김가나</v>
+        <v>강카타</v>
       </c>
       <c r="B51" t="str">
-        <v>19.05.12</v>
+        <v>19.09.03</v>
       </c>
       <c r="C51" t="str">
-        <v>2026.04.16</v>
+        <v>2026.05.15</v>
       </c>
       <c r="D51" t="str">
-        <v>09:00</v>
+        <v>10:40</v>
       </c>
       <c r="E51" t="str">
-        <v>09:50</v>
+        <v>11:30</v>
       </c>
       <c r="F51" t="str">
-        <v>2026.04.16</v>
+        <v>2026.05.15</v>
       </c>
       <c r="G51" t="str">
-        <v>09:52</v>
+        <v>11:32</v>
       </c>
       <c r="H51" t="str">
-        <v>500900007005</v>
+        <v>500900007045</v>
       </c>
       <c r="I51" t="str">
         <v>65,000</v>
@@ -2151,28 +2151,28 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>이다라</v>
+        <v>조바사</v>
       </c>
       <c r="B52" t="str">
-        <v>20.03.08</v>
+        <v>19.04.11</v>
       </c>
       <c r="C52" t="str">
-        <v>2026.04.16</v>
+        <v>2026.05.15</v>
       </c>
       <c r="D52" t="str">
-        <v>09:50</v>
+        <v>13:30</v>
       </c>
       <c r="E52" t="str">
-        <v>10:40</v>
+        <v>14:20</v>
       </c>
       <c r="F52" t="str">
-        <v>2026.04.16</v>
+        <v>2026.05.15</v>
       </c>
       <c r="G52" t="str">
-        <v>10:42</v>
+        <v>14:23</v>
       </c>
       <c r="H52" t="str">
-        <v>500900007013</v>
+        <v>500900007073</v>
       </c>
       <c r="I52" t="str">
         <v>65,000</v>
@@ -2186,28 +2186,28 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>박마바</v>
+        <v>한아자</v>
       </c>
       <c r="B53" t="str">
-        <v>18.11.22</v>
+        <v>20.10.21</v>
       </c>
       <c r="C53" t="str">
-        <v>2026.04.16</v>
+        <v>2026.05.15</v>
       </c>
       <c r="D53" t="str">
-        <v>10:40</v>
+        <v>15:10</v>
       </c>
       <c r="E53" t="str">
-        <v>11:30</v>
+        <v>16:00</v>
       </c>
       <c r="F53" t="str">
-        <v>2026.04.16</v>
+        <v>2026.05.15</v>
       </c>
       <c r="G53" t="str">
-        <v>11:32</v>
+        <v>16:03</v>
       </c>
       <c r="H53" t="str">
-        <v>500900007021</v>
+        <v>500900007081</v>
       </c>
       <c r="I53" t="str">
         <v>65,000</v>
@@ -2221,28 +2221,28 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>임가다</v>
+        <v>김가나</v>
       </c>
       <c r="B54" t="str">
-        <v>20.02.25</v>
+        <v>19.05.12</v>
       </c>
       <c r="C54" t="str">
-        <v>2026.04.16</v>
+        <v>2026.05.18</v>
       </c>
       <c r="D54" t="str">
-        <v>13:30</v>
+        <v>09:00</v>
       </c>
       <c r="E54" t="str">
-        <v>14:20</v>
+        <v>09:50</v>
       </c>
       <c r="F54" t="str">
-        <v>2026.04.16</v>
+        <v>2026.05.18</v>
       </c>
       <c r="G54" t="str">
-        <v>14:22</v>
+        <v>09:53</v>
       </c>
       <c r="H54" t="str">
-        <v>500900007057</v>
+        <v>500900007005</v>
       </c>
       <c r="I54" t="str">
         <v>65,000</v>
@@ -2256,28 +2256,28 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>송라마</v>
+        <v>이다라</v>
       </c>
       <c r="B55" t="str">
-        <v>21.06.07</v>
+        <v>20.03.08</v>
       </c>
       <c r="C55" t="str">
-        <v>2026.04.16</v>
+        <v>2026.05.18</v>
       </c>
       <c r="D55" t="str">
-        <v>14:20</v>
+        <v>09:50</v>
       </c>
       <c r="E55" t="str">
-        <v>15:10</v>
+        <v>10:40</v>
       </c>
       <c r="F55" t="str">
-        <v>2026.04.16</v>
+        <v>2026.05.18</v>
       </c>
       <c r="G55" t="str">
-        <v>15:12</v>
+        <v>10:42</v>
       </c>
       <c r="H55" t="str">
-        <v>500900007065</v>
+        <v>500900007013</v>
       </c>
       <c r="I55" t="str">
         <v>65,000</v>
@@ -2291,28 +2291,28 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>최사아</v>
+        <v>박마바</v>
       </c>
       <c r="B56" t="str">
-        <v>21.01.30</v>
+        <v>18.11.22</v>
       </c>
       <c r="C56" t="str">
-        <v>2026.04.17</v>
+        <v>2026.05.18</v>
       </c>
       <c r="D56" t="str">
-        <v>09:00</v>
+        <v>10:40</v>
       </c>
       <c r="E56" t="str">
-        <v>09:50</v>
+        <v>11:30</v>
       </c>
       <c r="F56" t="str">
-        <v>2026.04.17</v>
+        <v>2026.05.18</v>
       </c>
       <c r="G56" t="str">
-        <v>09:52</v>
+        <v>11:33</v>
       </c>
       <c r="H56" t="str">
-        <v>500900007029</v>
+        <v>500900007021</v>
       </c>
       <c r="I56" t="str">
         <v>65,000</v>
@@ -2326,28 +2326,28 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>정자차</v>
+        <v>임가다</v>
       </c>
       <c r="B57" t="str">
-        <v>20.07.14</v>
+        <v>20.02.25</v>
       </c>
       <c r="C57" t="str">
-        <v>2026.04.17</v>
+        <v>2026.05.18</v>
       </c>
       <c r="D57" t="str">
-        <v>09:50</v>
+        <v>13:30</v>
       </c>
       <c r="E57" t="str">
-        <v>10:40</v>
+        <v>14:20</v>
       </c>
       <c r="F57" t="str">
-        <v>2026.04.17</v>
+        <v>2026.05.18</v>
       </c>
       <c r="G57" t="str">
-        <v>10:42</v>
+        <v>14:23</v>
       </c>
       <c r="H57" t="str">
-        <v>500900007037</v>
+        <v>500900007057</v>
       </c>
       <c r="I57" t="str">
         <v>65,000</v>
@@ -2361,28 +2361,28 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>강카타</v>
+        <v>송라마</v>
       </c>
       <c r="B58" t="str">
-        <v>19.09.03</v>
+        <v>21.06.07</v>
       </c>
       <c r="C58" t="str">
-        <v>2026.04.17</v>
+        <v>2026.05.18</v>
       </c>
       <c r="D58" t="str">
-        <v>10:40</v>
+        <v>14:20</v>
       </c>
       <c r="E58" t="str">
-        <v>11:30</v>
+        <v>15:10</v>
       </c>
       <c r="F58" t="str">
-        <v>2026.04.17</v>
+        <v>2026.05.18</v>
       </c>
       <c r="G58" t="str">
-        <v>11:32</v>
+        <v>15:12</v>
       </c>
       <c r="H58" t="str">
-        <v>500900007045</v>
+        <v>500900007065</v>
       </c>
       <c r="I58" t="str">
         <v>65,000</v>
@@ -2396,28 +2396,28 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>조바사</v>
+        <v>최사아</v>
       </c>
       <c r="B59" t="str">
-        <v>19.04.11</v>
+        <v>21.01.30</v>
       </c>
       <c r="C59" t="str">
-        <v>2026.04.17</v>
+        <v>2026.05.19</v>
       </c>
       <c r="D59" t="str">
-        <v>13:30</v>
+        <v>09:00</v>
       </c>
       <c r="E59" t="str">
-        <v>14:20</v>
+        <v>09:50</v>
       </c>
       <c r="F59" t="str">
-        <v>2026.04.17</v>
+        <v>2026.05.19</v>
       </c>
       <c r="G59" t="str">
-        <v>14:22</v>
+        <v>09:53</v>
       </c>
       <c r="H59" t="str">
-        <v>500900007073</v>
+        <v>500900007030</v>
       </c>
       <c r="I59" t="str">
         <v>65,000</v>
@@ -2431,28 +2431,28 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>한아자</v>
+        <v>정자차</v>
       </c>
       <c r="B60" t="str">
-        <v>20.10.21</v>
+        <v>20.07.14</v>
       </c>
       <c r="C60" t="str">
-        <v>2026.04.17</v>
+        <v>2026.05.19</v>
       </c>
       <c r="D60" t="str">
-        <v>15:10</v>
+        <v>09:50</v>
       </c>
       <c r="E60" t="str">
-        <v>16:00</v>
+        <v>10:40</v>
       </c>
       <c r="F60" t="str">
-        <v>2026.04.17</v>
+        <v>2026.05.19</v>
       </c>
       <c r="G60" t="str">
-        <v>16:02</v>
+        <v>10:42</v>
       </c>
       <c r="H60" t="str">
-        <v>500900007081</v>
+        <v>500900007038</v>
       </c>
       <c r="I60" t="str">
         <v>65,000</v>
@@ -2466,28 +2466,28 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>김가나</v>
+        <v>강카타</v>
       </c>
       <c r="B61" t="str">
-        <v>19.05.12</v>
+        <v>19.09.03</v>
       </c>
       <c r="C61" t="str">
-        <v>2026.04.20</v>
+        <v>2026.05.19</v>
       </c>
       <c r="D61" t="str">
-        <v>09:00</v>
+        <v>10:40</v>
       </c>
       <c r="E61" t="str">
-        <v>09:50</v>
+        <v>11:30</v>
       </c>
       <c r="F61" t="str">
-        <v>2026.04.20</v>
+        <v>2026.05.19</v>
       </c>
       <c r="G61" t="str">
-        <v>09:53</v>
+        <v>11:33</v>
       </c>
       <c r="H61" t="str">
-        <v>500900007006</v>
+        <v>500900007046</v>
       </c>
       <c r="I61" t="str">
         <v>65,000</v>
@@ -2501,28 +2501,28 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>이다라</v>
+        <v>조바사</v>
       </c>
       <c r="B62" t="str">
-        <v>20.03.08</v>
+        <v>19.04.11</v>
       </c>
       <c r="C62" t="str">
-        <v>2026.04.20</v>
+        <v>2026.05.19</v>
       </c>
       <c r="D62" t="str">
-        <v>09:50</v>
+        <v>13:30</v>
       </c>
       <c r="E62" t="str">
-        <v>10:40</v>
+        <v>14:20</v>
       </c>
       <c r="F62" t="str">
-        <v>2026.04.20</v>
+        <v>2026.05.19</v>
       </c>
       <c r="G62" t="str">
-        <v>10:42</v>
+        <v>14:22</v>
       </c>
       <c r="H62" t="str">
-        <v>500900007014</v>
+        <v>500900007074</v>
       </c>
       <c r="I62" t="str">
         <v>65,000</v>
@@ -2536,28 +2536,28 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>박마바</v>
+        <v>한아자</v>
       </c>
       <c r="B63" t="str">
-        <v>18.11.22</v>
+        <v>20.10.21</v>
       </c>
       <c r="C63" t="str">
-        <v>2026.04.20</v>
+        <v>2026.05.19</v>
       </c>
       <c r="D63" t="str">
-        <v>10:40</v>
+        <v>15:10</v>
       </c>
       <c r="E63" t="str">
-        <v>11:30</v>
+        <v>16:00</v>
       </c>
       <c r="F63" t="str">
-        <v>2026.04.20</v>
+        <v>2026.05.19</v>
       </c>
       <c r="G63" t="str">
-        <v>11:32</v>
+        <v>16:02</v>
       </c>
       <c r="H63" t="str">
-        <v>500900007022</v>
+        <v>500900007082</v>
       </c>
       <c r="I63" t="str">
         <v>65,000</v>
@@ -2571,13 +2571,13 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>임가다</v>
+        <v>윤파하</v>
       </c>
       <c r="B64" t="str">
-        <v>20.02.25</v>
+        <v>17.12.18</v>
       </c>
       <c r="C64" t="str">
-        <v>2026.04.20</v>
+        <v>2026.05.20</v>
       </c>
       <c r="D64" t="str">
         <v>13:30</v>
@@ -2586,13 +2586,13 @@
         <v>14:20</v>
       </c>
       <c r="F64" t="str">
-        <v>2026.04.20</v>
+        <v>2026.05.20</v>
       </c>
       <c r="G64" t="str">
         <v>14:22</v>
       </c>
       <c r="H64" t="str">
-        <v>500900007058</v>
+        <v>500900007051</v>
       </c>
       <c r="I64" t="str">
         <v>65,000</v>
@@ -2606,28 +2606,28 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>송라마</v>
+        <v>백차카</v>
       </c>
       <c r="B65" t="str">
-        <v>21.06.07</v>
+        <v>18.08.05</v>
       </c>
       <c r="C65" t="str">
-        <v>2026.04.20</v>
+        <v>2026.05.20</v>
       </c>
       <c r="D65" t="str">
-        <v>14:20</v>
+        <v>16:00</v>
       </c>
       <c r="E65" t="str">
-        <v>15:10</v>
+        <v>16:50</v>
       </c>
       <c r="F65" t="str">
-        <v>2026.04.20</v>
+        <v>2026.05.20</v>
       </c>
       <c r="G65" t="str">
-        <v>15:13</v>
+        <v>16:53</v>
       </c>
       <c r="H65" t="str">
-        <v>500900007066</v>
+        <v>500900007087</v>
       </c>
       <c r="I65" t="str">
         <v>65,000</v>
@@ -2641,13 +2641,13 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>최사아</v>
+        <v>김가나</v>
       </c>
       <c r="B66" t="str">
-        <v>21.01.30</v>
+        <v>19.05.12</v>
       </c>
       <c r="C66" t="str">
-        <v>2026.04.21</v>
+        <v>2026.05.21</v>
       </c>
       <c r="D66" t="str">
         <v>09:00</v>
@@ -2656,13 +2656,13 @@
         <v>09:50</v>
       </c>
       <c r="F66" t="str">
-        <v>2026.04.21</v>
+        <v>2026.05.21</v>
       </c>
       <c r="G66" t="str">
         <v>09:52</v>
       </c>
       <c r="H66" t="str">
-        <v>500900007030</v>
+        <v>500900007006</v>
       </c>
       <c r="I66" t="str">
         <v>65,000</v>
@@ -2676,13 +2676,13 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>정자차</v>
+        <v>이다라</v>
       </c>
       <c r="B67" t="str">
-        <v>20.07.14</v>
+        <v>20.03.08</v>
       </c>
       <c r="C67" t="str">
-        <v>2026.04.21</v>
+        <v>2026.05.21</v>
       </c>
       <c r="D67" t="str">
         <v>09:50</v>
@@ -2691,13 +2691,13 @@
         <v>10:40</v>
       </c>
       <c r="F67" t="str">
-        <v>2026.04.21</v>
+        <v>2026.05.21</v>
       </c>
       <c r="G67" t="str">
-        <v>10:42</v>
+        <v>10:43</v>
       </c>
       <c r="H67" t="str">
-        <v>500900007038</v>
+        <v>500900007014</v>
       </c>
       <c r="I67" t="str">
         <v>65,000</v>
@@ -2711,13 +2711,13 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>강카타</v>
+        <v>박마바</v>
       </c>
       <c r="B68" t="str">
-        <v>19.09.03</v>
+        <v>18.11.22</v>
       </c>
       <c r="C68" t="str">
-        <v>2026.04.21</v>
+        <v>2026.05.21</v>
       </c>
       <c r="D68" t="str">
         <v>10:40</v>
@@ -2726,13 +2726,13 @@
         <v>11:30</v>
       </c>
       <c r="F68" t="str">
-        <v>2026.04.21</v>
+        <v>2026.05.21</v>
       </c>
       <c r="G68" t="str">
         <v>11:32</v>
       </c>
       <c r="H68" t="str">
-        <v>500900007046</v>
+        <v>500900007022</v>
       </c>
       <c r="I68" t="str">
         <v>65,000</v>
@@ -2746,13 +2746,13 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>조바사</v>
+        <v>임가다</v>
       </c>
       <c r="B69" t="str">
-        <v>19.04.11</v>
+        <v>20.02.25</v>
       </c>
       <c r="C69" t="str">
-        <v>2026.04.21</v>
+        <v>2026.05.21</v>
       </c>
       <c r="D69" t="str">
         <v>13:30</v>
@@ -2761,13 +2761,13 @@
         <v>14:20</v>
       </c>
       <c r="F69" t="str">
-        <v>2026.04.21</v>
+        <v>2026.05.21</v>
       </c>
       <c r="G69" t="str">
-        <v>14:22</v>
+        <v>14:23</v>
       </c>
       <c r="H69" t="str">
-        <v>500900007074</v>
+        <v>500900007058</v>
       </c>
       <c r="I69" t="str">
         <v>65,000</v>
@@ -2781,28 +2781,28 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>한아자</v>
+        <v>송라마</v>
       </c>
       <c r="B70" t="str">
-        <v>20.10.21</v>
+        <v>21.06.07</v>
       </c>
       <c r="C70" t="str">
-        <v>2026.04.21</v>
+        <v>2026.05.21</v>
       </c>
       <c r="D70" t="str">
+        <v>14:20</v>
+      </c>
+      <c r="E70" t="str">
         <v>15:10</v>
       </c>
-      <c r="E70" t="str">
-        <v>16:00</v>
-      </c>
       <c r="F70" t="str">
-        <v>2026.04.21</v>
+        <v>2026.05.21</v>
       </c>
       <c r="G70" t="str">
-        <v>16:02</v>
+        <v>15:13</v>
       </c>
       <c r="H70" t="str">
-        <v>500900007082</v>
+        <v>500900007066</v>
       </c>
       <c r="I70" t="str">
         <v>65,000</v>
@@ -2816,28 +2816,28 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>윤파하</v>
+        <v>최사아</v>
       </c>
       <c r="B71" t="str">
-        <v>17.12.18</v>
+        <v>21.01.30</v>
       </c>
       <c r="C71" t="str">
-        <v>2026.04.22</v>
+        <v>2026.05.22</v>
       </c>
       <c r="D71" t="str">
-        <v>13:30</v>
+        <v>09:00</v>
       </c>
       <c r="E71" t="str">
-        <v>14:20</v>
+        <v>09:50</v>
       </c>
       <c r="F71" t="str">
-        <v>2026.04.22</v>
+        <v>2026.05.22</v>
       </c>
       <c r="G71" t="str">
-        <v>14:22</v>
+        <v>09:53</v>
       </c>
       <c r="H71" t="str">
-        <v>500900007052</v>
+        <v>500900007031</v>
       </c>
       <c r="I71" t="str">
         <v>65,000</v>
@@ -2851,28 +2851,28 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>백차카</v>
+        <v>정자차</v>
       </c>
       <c r="B72" t="str">
-        <v>18.08.05</v>
+        <v>20.07.14</v>
       </c>
       <c r="C72" t="str">
-        <v>2026.04.22</v>
+        <v>2026.05.22</v>
       </c>
       <c r="D72" t="str">
-        <v>16:00</v>
+        <v>09:50</v>
       </c>
       <c r="E72" t="str">
-        <v>16:50</v>
+        <v>10:40</v>
       </c>
       <c r="F72" t="str">
-        <v>2026.04.22</v>
+        <v>2026.05.22</v>
       </c>
       <c r="G72" t="str">
-        <v>16:52</v>
+        <v>10:43</v>
       </c>
       <c r="H72" t="str">
-        <v>500900007088</v>
+        <v>500900007039</v>
       </c>
       <c r="I72" t="str">
         <v>65,000</v>
@@ -2886,28 +2886,28 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>김가나</v>
+        <v>강카타</v>
       </c>
       <c r="B73" t="str">
-        <v>19.05.12</v>
+        <v>19.09.03</v>
       </c>
       <c r="C73" t="str">
-        <v>2026.04.23</v>
+        <v>2026.05.22</v>
       </c>
       <c r="D73" t="str">
-        <v>09:00</v>
+        <v>10:40</v>
       </c>
       <c r="E73" t="str">
-        <v>09:50</v>
+        <v>11:30</v>
       </c>
       <c r="F73" t="str">
-        <v>2026.04.23</v>
+        <v>2026.05.22</v>
       </c>
       <c r="G73" t="str">
-        <v>09:53</v>
+        <v>11:33</v>
       </c>
       <c r="H73" t="str">
-        <v>500900007007</v>
+        <v>500900007047</v>
       </c>
       <c r="I73" t="str">
         <v>65,000</v>
@@ -2921,28 +2921,28 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>이다라</v>
+        <v>조바사</v>
       </c>
       <c r="B74" t="str">
-        <v>20.03.08</v>
+        <v>19.04.11</v>
       </c>
       <c r="C74" t="str">
-        <v>2026.04.23</v>
+        <v>2026.05.22</v>
       </c>
       <c r="D74" t="str">
-        <v>09:50</v>
+        <v>13:30</v>
       </c>
       <c r="E74" t="str">
-        <v>10:40</v>
+        <v>14:20</v>
       </c>
       <c r="F74" t="str">
-        <v>2026.04.23</v>
+        <v>2026.05.22</v>
       </c>
       <c r="G74" t="str">
-        <v>10:42</v>
+        <v>14:22</v>
       </c>
       <c r="H74" t="str">
-        <v>500900007015</v>
+        <v>500900007075</v>
       </c>
       <c r="I74" t="str">
         <v>65,000</v>
@@ -2956,28 +2956,28 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>박마바</v>
+        <v>한아자</v>
       </c>
       <c r="B75" t="str">
-        <v>18.11.22</v>
+        <v>20.10.21</v>
       </c>
       <c r="C75" t="str">
-        <v>2026.04.23</v>
+        <v>2026.05.22</v>
       </c>
       <c r="D75" t="str">
-        <v>10:40</v>
+        <v>15:10</v>
       </c>
       <c r="E75" t="str">
-        <v>11:30</v>
+        <v>16:00</v>
       </c>
       <c r="F75" t="str">
-        <v>2026.04.23</v>
+        <v>2026.05.22</v>
       </c>
       <c r="G75" t="str">
-        <v>11:33</v>
+        <v>16:02</v>
       </c>
       <c r="H75" t="str">
-        <v>500900007023</v>
+        <v>500900007083</v>
       </c>
       <c r="I75" t="str">
         <v>65,000</v>
@@ -2991,28 +2991,28 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>임가다</v>
+        <v>김가나</v>
       </c>
       <c r="B76" t="str">
-        <v>20.02.25</v>
+        <v>19.05.12</v>
       </c>
       <c r="C76" t="str">
-        <v>2026.04.23</v>
+        <v>2026.05.25</v>
       </c>
       <c r="D76" t="str">
-        <v>13:30</v>
+        <v>09:00</v>
       </c>
       <c r="E76" t="str">
-        <v>14:20</v>
+        <v>09:50</v>
       </c>
       <c r="F76" t="str">
-        <v>2026.04.23</v>
+        <v>2026.05.25</v>
       </c>
       <c r="G76" t="str">
-        <v>14:23</v>
+        <v>09:53</v>
       </c>
       <c r="H76" t="str">
-        <v>500900007059</v>
+        <v>500900007007</v>
       </c>
       <c r="I76" t="str">
         <v>65,000</v>
@@ -3026,28 +3026,28 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>송라마</v>
+        <v>이다라</v>
       </c>
       <c r="B77" t="str">
-        <v>21.06.07</v>
+        <v>20.03.08</v>
       </c>
       <c r="C77" t="str">
-        <v>2026.04.23</v>
+        <v>2026.05.25</v>
       </c>
       <c r="D77" t="str">
-        <v>14:20</v>
+        <v>09:50</v>
       </c>
       <c r="E77" t="str">
-        <v>15:10</v>
+        <v>10:40</v>
       </c>
       <c r="F77" t="str">
-        <v>2026.04.23</v>
+        <v>2026.05.25</v>
       </c>
       <c r="G77" t="str">
-        <v>15:13</v>
+        <v>10:42</v>
       </c>
       <c r="H77" t="str">
-        <v>500900007067</v>
+        <v>500900007015</v>
       </c>
       <c r="I77" t="str">
         <v>65,000</v>
@@ -3061,28 +3061,28 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>최사아</v>
+        <v>박마바</v>
       </c>
       <c r="B78" t="str">
-        <v>21.01.30</v>
+        <v>18.11.22</v>
       </c>
       <c r="C78" t="str">
-        <v>2026.04.24</v>
+        <v>2026.05.25</v>
       </c>
       <c r="D78" t="str">
-        <v>09:00</v>
+        <v>10:40</v>
       </c>
       <c r="E78" t="str">
-        <v>09:50</v>
+        <v>11:30</v>
       </c>
       <c r="F78" t="str">
-        <v>2026.04.24</v>
+        <v>2026.05.25</v>
       </c>
       <c r="G78" t="str">
-        <v>09:53</v>
+        <v>11:33</v>
       </c>
       <c r="H78" t="str">
-        <v>500900007031</v>
+        <v>500900007023</v>
       </c>
       <c r="I78" t="str">
         <v>65,000</v>
@@ -3096,28 +3096,28 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>정자차</v>
+        <v>임가다</v>
       </c>
       <c r="B79" t="str">
-        <v>20.07.14</v>
+        <v>20.02.25</v>
       </c>
       <c r="C79" t="str">
-        <v>2026.04.24</v>
+        <v>2026.05.25</v>
       </c>
       <c r="D79" t="str">
-        <v>09:50</v>
+        <v>13:30</v>
       </c>
       <c r="E79" t="str">
-        <v>10:40</v>
+        <v>14:20</v>
       </c>
       <c r="F79" t="str">
-        <v>2026.04.24</v>
+        <v>2026.05.25</v>
       </c>
       <c r="G79" t="str">
-        <v>10:43</v>
+        <v>14:23</v>
       </c>
       <c r="H79" t="str">
-        <v>500900007039</v>
+        <v>500900007059</v>
       </c>
       <c r="I79" t="str">
         <v>65,000</v>
@@ -3131,28 +3131,28 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>강카타</v>
+        <v>송라마</v>
       </c>
       <c r="B80" t="str">
-        <v>19.09.03</v>
+        <v>21.06.07</v>
       </c>
       <c r="C80" t="str">
-        <v>2026.04.24</v>
+        <v>2026.05.25</v>
       </c>
       <c r="D80" t="str">
-        <v>10:40</v>
+        <v>14:20</v>
       </c>
       <c r="E80" t="str">
-        <v>11:30</v>
+        <v>15:10</v>
       </c>
       <c r="F80" t="str">
-        <v>2026.04.24</v>
+        <v>2026.05.25</v>
       </c>
       <c r="G80" t="str">
-        <v>11:32</v>
+        <v>15:13</v>
       </c>
       <c r="H80" t="str">
-        <v>500900007047</v>
+        <v>500900007067</v>
       </c>
       <c r="I80" t="str">
         <v>65,000</v>
@@ -3166,28 +3166,28 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>조바사</v>
+        <v>최사아</v>
       </c>
       <c r="B81" t="str">
-        <v>19.04.11</v>
+        <v>21.01.30</v>
       </c>
       <c r="C81" t="str">
-        <v>2026.04.24</v>
+        <v>2026.05.26</v>
       </c>
       <c r="D81" t="str">
-        <v>13:30</v>
+        <v>09:00</v>
       </c>
       <c r="E81" t="str">
-        <v>14:20</v>
+        <v>09:50</v>
       </c>
       <c r="F81" t="str">
-        <v>2026.04.24</v>
+        <v>2026.05.26</v>
       </c>
       <c r="G81" t="str">
-        <v>14:23</v>
+        <v>09:52</v>
       </c>
       <c r="H81" t="str">
-        <v>500900007075</v>
+        <v>500900007032</v>
       </c>
       <c r="I81" t="str">
         <v>65,000</v>
@@ -3201,28 +3201,28 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>한아자</v>
+        <v>정자차</v>
       </c>
       <c r="B82" t="str">
-        <v>20.10.21</v>
+        <v>20.07.14</v>
       </c>
       <c r="C82" t="str">
-        <v>2026.04.24</v>
+        <v>2026.05.26</v>
       </c>
       <c r="D82" t="str">
-        <v>15:10</v>
+        <v>09:50</v>
       </c>
       <c r="E82" t="str">
-        <v>16:00</v>
+        <v>10:40</v>
       </c>
       <c r="F82" t="str">
-        <v>2026.04.24</v>
+        <v>2026.05.26</v>
       </c>
       <c r="G82" t="str">
-        <v>16:03</v>
+        <v>10:42</v>
       </c>
       <c r="H82" t="str">
-        <v>500900007083</v>
+        <v>500900007040</v>
       </c>
       <c r="I82" t="str">
         <v>65,000</v>
@@ -3236,28 +3236,28 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>김가나</v>
+        <v>강카타</v>
       </c>
       <c r="B83" t="str">
-        <v>19.05.12</v>
+        <v>19.09.03</v>
       </c>
       <c r="C83" t="str">
-        <v>2026.04.27</v>
+        <v>2026.05.26</v>
       </c>
       <c r="D83" t="str">
-        <v>09:00</v>
+        <v>10:40</v>
       </c>
       <c r="E83" t="str">
-        <v>09:50</v>
+        <v>11:30</v>
       </c>
       <c r="F83" t="str">
-        <v>2026.04.27</v>
+        <v>2026.05.26</v>
       </c>
       <c r="G83" t="str">
-        <v>09:52</v>
+        <v>11:32</v>
       </c>
       <c r="H83" t="str">
-        <v>500900007008</v>
+        <v>500900007048</v>
       </c>
       <c r="I83" t="str">
         <v>65,000</v>
@@ -3271,28 +3271,28 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>이다라</v>
+        <v>조바사</v>
       </c>
       <c r="B84" t="str">
-        <v>20.03.08</v>
+        <v>19.04.11</v>
       </c>
       <c r="C84" t="str">
-        <v>2026.04.27</v>
+        <v>2026.05.26</v>
       </c>
       <c r="D84" t="str">
-        <v>09:50</v>
+        <v>13:30</v>
       </c>
       <c r="E84" t="str">
-        <v>10:40</v>
+        <v>14:20</v>
       </c>
       <c r="F84" t="str">
-        <v>2026.04.27</v>
+        <v>2026.05.26</v>
       </c>
       <c r="G84" t="str">
-        <v>10:43</v>
+        <v>14:23</v>
       </c>
       <c r="H84" t="str">
-        <v>500900007016</v>
+        <v>500900007076</v>
       </c>
       <c r="I84" t="str">
         <v>65,000</v>
@@ -3306,28 +3306,28 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>박마바</v>
+        <v>한아자</v>
       </c>
       <c r="B85" t="str">
-        <v>18.11.22</v>
+        <v>20.10.21</v>
       </c>
       <c r="C85" t="str">
-        <v>2026.04.27</v>
+        <v>2026.05.26</v>
       </c>
       <c r="D85" t="str">
-        <v>10:40</v>
+        <v>15:10</v>
       </c>
       <c r="E85" t="str">
-        <v>11:30</v>
+        <v>16:00</v>
       </c>
       <c r="F85" t="str">
-        <v>2026.04.27</v>
+        <v>2026.05.26</v>
       </c>
       <c r="G85" t="str">
-        <v>11:32</v>
+        <v>16:02</v>
       </c>
       <c r="H85" t="str">
-        <v>500900007024</v>
+        <v>500900007084</v>
       </c>
       <c r="I85" t="str">
         <v>65,000</v>
@@ -3341,13 +3341,13 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>임가다</v>
+        <v>윤파하</v>
       </c>
       <c r="B86" t="str">
-        <v>20.02.25</v>
+        <v>17.12.18</v>
       </c>
       <c r="C86" t="str">
-        <v>2026.04.27</v>
+        <v>2026.05.27</v>
       </c>
       <c r="D86" t="str">
         <v>13:30</v>
@@ -3356,13 +3356,13 @@
         <v>14:20</v>
       </c>
       <c r="F86" t="str">
-        <v>2026.04.27</v>
+        <v>2026.05.27</v>
       </c>
       <c r="G86" t="str">
         <v>14:22</v>
       </c>
       <c r="H86" t="str">
-        <v>500900007060</v>
+        <v>500900007052</v>
       </c>
       <c r="I86" t="str">
         <v>65,000</v>
@@ -3376,28 +3376,28 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>송라마</v>
+        <v>백차카</v>
       </c>
       <c r="B87" t="str">
-        <v>21.06.07</v>
+        <v>18.08.05</v>
       </c>
       <c r="C87" t="str">
-        <v>2026.04.27</v>
+        <v>2026.05.27</v>
       </c>
       <c r="D87" t="str">
-        <v>14:20</v>
+        <v>16:00</v>
       </c>
       <c r="E87" t="str">
-        <v>15:10</v>
+        <v>16:50</v>
       </c>
       <c r="F87" t="str">
-        <v>2026.04.27</v>
+        <v>2026.05.27</v>
       </c>
       <c r="G87" t="str">
-        <v>15:12</v>
+        <v>16:53</v>
       </c>
       <c r="H87" t="str">
-        <v>500900007068</v>
+        <v>500900007088</v>
       </c>
       <c r="I87" t="str">
         <v>65,000</v>
@@ -3411,13 +3411,13 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>최사아</v>
+        <v>김가나</v>
       </c>
       <c r="B88" t="str">
-        <v>21.01.30</v>
+        <v>19.05.12</v>
       </c>
       <c r="C88" t="str">
-        <v>2026.04.28</v>
+        <v>2026.05.28</v>
       </c>
       <c r="D88" t="str">
         <v>09:00</v>
@@ -3426,13 +3426,13 @@
         <v>09:50</v>
       </c>
       <c r="F88" t="str">
-        <v>2026.04.28</v>
+        <v>2026.05.28</v>
       </c>
       <c r="G88" t="str">
         <v>09:53</v>
       </c>
       <c r="H88" t="str">
-        <v>500900007032</v>
+        <v>500900007008</v>
       </c>
       <c r="I88" t="str">
         <v>65,000</v>
@@ -3446,13 +3446,13 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>정자차</v>
+        <v>이다라</v>
       </c>
       <c r="B89" t="str">
-        <v>20.07.14</v>
+        <v>20.03.08</v>
       </c>
       <c r="C89" t="str">
-        <v>2026.04.28</v>
+        <v>2026.05.28</v>
       </c>
       <c r="D89" t="str">
         <v>09:50</v>
@@ -3461,13 +3461,13 @@
         <v>10:40</v>
       </c>
       <c r="F89" t="str">
-        <v>2026.04.28</v>
+        <v>2026.05.28</v>
       </c>
       <c r="G89" t="str">
         <v>10:42</v>
       </c>
       <c r="H89" t="str">
-        <v>500900007040</v>
+        <v>500900007016</v>
       </c>
       <c r="I89" t="str">
         <v>65,000</v>
@@ -3481,13 +3481,13 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>강카타</v>
+        <v>박마바</v>
       </c>
       <c r="B90" t="str">
-        <v>19.09.03</v>
+        <v>18.11.22</v>
       </c>
       <c r="C90" t="str">
-        <v>2026.04.28</v>
+        <v>2026.05.28</v>
       </c>
       <c r="D90" t="str">
         <v>10:40</v>
@@ -3496,19 +3496,19 @@
         <v>11:30</v>
       </c>
       <c r="F90" t="str">
-        <v>2026.04.28</v>
+        <v>2026.05.28</v>
       </c>
       <c r="G90" t="str">
         <v>11:33</v>
       </c>
       <c r="H90" t="str">
-        <v>500900007048</v>
+        <v>500900007024</v>
       </c>
       <c r="I90" t="str">
         <v>65,000</v>
       </c>
       <c r="J90" t="str">
-        <v>정상결제</v>
+        <v>소급결제</v>
       </c>
       <c r="K90" t="str">
         <v>꿈나라발달언어센터</v>
@@ -3516,13 +3516,13 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>조바사</v>
+        <v>임가다</v>
       </c>
       <c r="B91" t="str">
-        <v>19.04.11</v>
+        <v>20.02.25</v>
       </c>
       <c r="C91" t="str">
-        <v>2026.04.28</v>
+        <v>2026.05.28</v>
       </c>
       <c r="D91" t="str">
         <v>13:30</v>
@@ -3531,19 +3531,19 @@
         <v>14:20</v>
       </c>
       <c r="F91" t="str">
-        <v>2026.04.28</v>
+        <v>2026.05.28</v>
       </c>
       <c r="G91" t="str">
-        <v>14:22</v>
+        <v>14:23</v>
       </c>
       <c r="H91" t="str">
-        <v>500900007076</v>
+        <v>500900007060</v>
       </c>
       <c r="I91" t="str">
         <v>65,000</v>
       </c>
       <c r="J91" t="str">
-        <v>정상결제</v>
+        <v>소급결제</v>
       </c>
       <c r="K91" t="str">
         <v>꿈나라발달언어센터</v>
@@ -3551,28 +3551,28 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>한아자</v>
+        <v>송라마</v>
       </c>
       <c r="B92" t="str">
-        <v>20.10.21</v>
+        <v>21.06.07</v>
       </c>
       <c r="C92" t="str">
-        <v>2026.04.28</v>
+        <v>2026.05.28</v>
       </c>
       <c r="D92" t="str">
+        <v>14:20</v>
+      </c>
+      <c r="E92" t="str">
         <v>15:10</v>
       </c>
-      <c r="E92" t="str">
-        <v>16:00</v>
-      </c>
       <c r="F92" t="str">
-        <v>2026.04.28</v>
+        <v>2026.05.28</v>
       </c>
       <c r="G92" t="str">
-        <v>16:02</v>
+        <v>15:13</v>
       </c>
       <c r="H92" t="str">
-        <v>500900007084</v>
+        <v>500900007068</v>
       </c>
       <c r="I92" t="str">
         <v>65,000</v>
